--- a/src/assets/LPPI-LPF.xlsx
+++ b/src/assets/LPPI-LPF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\czari\Documents\GitHub\OCGEMPC\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43D0F2C-88BC-48C1-BC93-120C9643672D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CF7DDD-809E-4F72-8510-04E98DA2F030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A4379B76-126F-4F24-844E-2F6626CD5DC6}"/>
   </bookViews>
@@ -18,13 +18,21 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$M$52</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -209,7 +217,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,12 +270,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Aptos Narrow"/>
@@ -435,7 +437,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -550,9 +552,6 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -565,14 +564,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -589,7 +580,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -607,21 +598,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1104,26 +1091,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C3C966B-8316-453A-995B-EE6E00911D05}">
   <dimension ref="A2:O52"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.09765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.09765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.59765625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.296875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="13.3984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.59765625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="13" style="6" customWidth="1"/>
-    <col min="13" max="13" width="11.59765625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.09765625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.09765625" style="1"/>
+    <col min="13" max="13" width="11.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.109375" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1137,7 +1124,7 @@
       <c r="K2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1152,49 +1139,49 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-    </row>
-    <row r="7" spans="1:14" ht="5.25" customHeight="1">
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+    </row>
+    <row r="7" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="8"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1">
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="8"/>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-    </row>
-    <row r="9" spans="1:14" ht="6.75" customHeight="1">
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="52"/>
+    </row>
+    <row r="9" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="8"/>
       <c r="F9" s="6"/>
@@ -1203,30 +1190,30 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:14" ht="13.8">
+    <row r="10" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="8"/>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
       <c r="F10" s="3"/>
       <c r="J10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="57" t="s">
+      <c r="K10" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="58"/>
-      <c r="M10" s="59"/>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="54"/>
+      <c r="M10" s="55"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -1250,7 +1237,7 @@
         <v>1.0416666666666667</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="3"/>
@@ -1265,72 +1252,72 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="18" customFormat="1">
+    <row r="14" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="F14" s="19"/>
       <c r="G14" s="20"/>
       <c r="H14" s="21"/>
       <c r="L14" s="22"/>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="60" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="63" t="s">
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="64"/>
-      <c r="M15" s="64"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="61"/>
-      <c r="B16" s="65" t="s">
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="60"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="57"/>
+      <c r="B16" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="60" t="s">
+      <c r="D16" s="60"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="72" t="s">
+      <c r="G16" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="74" t="s">
+      <c r="H16" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="65" t="s">
+      <c r="I16" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="65" t="s">
+      <c r="J16" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="65" t="s">
+      <c r="K16" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="L16" s="76" t="s">
+      <c r="L16" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="65" t="s">
+      <c r="M16" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="N16" s="68"/>
-    </row>
-    <row r="17" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A17" s="62"/>
-      <c r="B17" s="66"/>
+      <c r="N16" s="64"/>
+    </row>
+    <row r="17" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="58"/>
+      <c r="B17" s="62"/>
       <c r="C17" s="23" t="s">
         <v>27</v>
       </c>
@@ -1340,17 +1327,17 @@
       <c r="E17" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="66"/>
-      <c r="N17" s="68"/>
-    </row>
-    <row r="18" spans="1:15" ht="24" customHeight="1">
+      <c r="F17" s="58"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="64"/>
+    </row>
+    <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24"/>
       <c r="B18" s="25"/>
       <c r="C18" s="26"/>
@@ -1362,14 +1349,14 @@
       <c r="I18" s="27"/>
       <c r="J18" s="27"/>
       <c r="K18" s="30"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="52"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="48"/>
       <c r="O18" s="31">
         <f>IF(K18&gt;2,K18,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="24" customHeight="1">
+    <row r="19" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="24"/>
       <c r="B19" s="25"/>
       <c r="C19" s="26"/>
@@ -1382,13 +1369,13 @@
       <c r="J19" s="27"/>
       <c r="K19" s="30"/>
       <c r="L19" s="25"/>
-      <c r="M19" s="52"/>
+      <c r="M19" s="48"/>
       <c r="O19" s="31">
         <f>IF(K19&gt;2,K19,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="24" customHeight="1">
+    <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="24"/>
       <c r="B20" s="25"/>
       <c r="C20" s="26"/>
@@ -1401,13 +1388,13 @@
       <c r="J20" s="27"/>
       <c r="K20" s="30"/>
       <c r="L20" s="25"/>
-      <c r="M20" s="52"/>
-      <c r="O20" s="32">
+      <c r="M20" s="48"/>
+      <c r="O20" s="31">
         <f t="shared" ref="O20:O30" si="0">IF(K20&gt;2,K20,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="24" customHeight="1">
+    <row r="21" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="24"/>
       <c r="B21" s="25"/>
       <c r="C21" s="26"/>
@@ -1420,18 +1407,18 @@
       <c r="J21" s="27"/>
       <c r="K21" s="30"/>
       <c r="L21" s="25"/>
-      <c r="M21" s="52"/>
-      <c r="O21" s="32">
+      <c r="M21" s="48"/>
+      <c r="O21" s="31">
         <f>IF(K21&gt;2,K21,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="24" customHeight="1">
+    <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24"/>
       <c r="B22" s="25"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="27"/>
       <c r="G22" s="28"/>
       <c r="H22" s="29"/>
@@ -1439,18 +1426,18 @@
       <c r="J22" s="27"/>
       <c r="K22" s="30"/>
       <c r="L22" s="25"/>
-      <c r="M22" s="52"/>
-      <c r="O22" s="32">
+      <c r="M22" s="48"/>
+      <c r="O22" s="31">
         <f>IF(K22&gt;2,K22,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="24" customHeight="1">
+    <row r="23" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
       <c r="F23" s="27"/>
       <c r="G23" s="28"/>
       <c r="H23" s="29"/>
@@ -1458,18 +1445,18 @@
       <c r="J23" s="27"/>
       <c r="K23" s="30"/>
       <c r="L23" s="25"/>
-      <c r="M23" s="52"/>
-      <c r="O23" s="32">
+      <c r="M23" s="48"/>
+      <c r="O23" s="31">
         <f>IF(K23&gt;2,K23,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="28.5" customHeight="1">
+    <row r="24" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="24"/>
       <c r="B24" s="25"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
       <c r="F24" s="27"/>
       <c r="G24" s="28"/>
       <c r="H24" s="29"/>
@@ -1477,18 +1464,18 @@
       <c r="J24" s="27"/>
       <c r="K24" s="30"/>
       <c r="L24" s="25"/>
-      <c r="M24" s="52"/>
-      <c r="O24" s="32">
+      <c r="M24" s="48"/>
+      <c r="O24" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="27.75" customHeight="1">
+    <row r="25" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="24"/>
       <c r="B25" s="25"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
       <c r="F25" s="27"/>
       <c r="G25" s="28"/>
       <c r="H25" s="29"/>
@@ -1496,13 +1483,13 @@
       <c r="J25" s="27"/>
       <c r="K25" s="30"/>
       <c r="L25" s="25"/>
-      <c r="M25" s="52"/>
-      <c r="O25" s="32">
+      <c r="M25" s="48"/>
+      <c r="O25" s="31">
         <f>IF(K25&gt;2,K25,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="28.5" customHeight="1">
+    <row r="26" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="24"/>
       <c r="B26" s="25"/>
       <c r="C26" s="26"/>
@@ -1515,13 +1502,13 @@
       <c r="J26" s="27"/>
       <c r="K26" s="30"/>
       <c r="L26" s="25"/>
-      <c r="M26" s="52"/>
-      <c r="O26" s="32">
+      <c r="M26" s="48"/>
+      <c r="O26" s="31">
         <f>IF(K26&gt;2,K26,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="24" customHeight="1">
+    <row r="27" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="24"/>
       <c r="B27" s="25"/>
       <c r="C27" s="26"/>
@@ -1534,18 +1521,18 @@
       <c r="J27" s="27"/>
       <c r="K27" s="30"/>
       <c r="L27" s="25"/>
-      <c r="M27" s="52"/>
-      <c r="O27" s="32">
+      <c r="M27" s="48"/>
+      <c r="O27" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="24.75" customHeight="1">
+    <row r="28" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="24"/>
       <c r="B28" s="25"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="34"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="27"/>
       <c r="G28" s="28"/>
       <c r="H28" s="29"/>
@@ -1553,18 +1540,18 @@
       <c r="J28" s="27"/>
       <c r="K28" s="30"/>
       <c r="L28" s="25"/>
-      <c r="M28" s="52"/>
+      <c r="M28" s="48"/>
       <c r="O28" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="24" customHeight="1">
+    <row r="29" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="24"/>
       <c r="B29" s="25"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
-      <c r="E29" s="34"/>
+      <c r="E29" s="33"/>
       <c r="F29" s="27"/>
       <c r="G29" s="28"/>
       <c r="H29" s="29"/>
@@ -1572,18 +1559,18 @@
       <c r="J29" s="27"/>
       <c r="K29" s="30"/>
       <c r="L29" s="25"/>
-      <c r="M29" s="52"/>
+      <c r="M29" s="48"/>
       <c r="O29" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="24" customHeight="1">
+    <row r="30" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="24"/>
       <c r="B30" s="25"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
-      <c r="E30" s="34"/>
+      <c r="E30" s="33"/>
       <c r="F30" s="27"/>
       <c r="G30" s="28"/>
       <c r="H30" s="29"/>
@@ -1591,18 +1578,18 @@
       <c r="J30" s="27"/>
       <c r="K30" s="30"/>
       <c r="L30" s="25"/>
-      <c r="M30" s="52"/>
-      <c r="O30" s="32">
+      <c r="M30" s="48"/>
+      <c r="O30" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="24" customHeight="1">
+    <row r="31" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="24"/>
       <c r="B31" s="25"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
-      <c r="E31" s="33"/>
+      <c r="E31" s="32"/>
       <c r="F31" s="27"/>
       <c r="G31" s="28"/>
       <c r="H31" s="29"/>
@@ -1610,13 +1597,13 @@
       <c r="J31" s="27"/>
       <c r="K31" s="30"/>
       <c r="L31" s="25"/>
-      <c r="M31" s="52"/>
-      <c r="O31" s="32">
+      <c r="M31" s="48"/>
+      <c r="O31" s="31">
         <f t="shared" ref="O31:O35" si="1">IF(K32&gt;2,K32,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="25.5" customHeight="1">
+    <row r="32" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="24"/>
       <c r="B32" s="25"/>
       <c r="C32" s="14"/>
@@ -1629,13 +1616,13 @@
       <c r="J32" s="27"/>
       <c r="K32" s="30"/>
       <c r="L32" s="25"/>
-      <c r="M32" s="52"/>
-      <c r="O32" s="32">
+      <c r="M32" s="48"/>
+      <c r="O32" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="24" customHeight="1">
+    <row r="33" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="24"/>
       <c r="B33" s="25"/>
       <c r="C33" s="26"/>
@@ -1648,13 +1635,13 @@
       <c r="J33" s="27"/>
       <c r="K33" s="30"/>
       <c r="L33" s="25"/>
-      <c r="M33" s="52"/>
-      <c r="O33" s="32">
+      <c r="M33" s="48"/>
+      <c r="O33" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="24" customHeight="1">
+    <row r="34" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="24"/>
       <c r="B34" s="25"/>
       <c r="C34" s="26"/>
@@ -1662,18 +1649,18 @@
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
-      <c r="H34" s="35"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="27"/>
       <c r="J34" s="27"/>
       <c r="K34" s="30"/>
       <c r="L34" s="25"/>
-      <c r="M34" s="52"/>
-      <c r="O34" s="32">
+      <c r="M34" s="48"/>
+      <c r="O34" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="24" customHeight="1">
+    <row r="35" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="24"/>
       <c r="B35" s="25"/>
       <c r="C35" s="26"/>
@@ -1681,56 +1668,56 @@
       <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="28"/>
-      <c r="H35" s="35"/>
+      <c r="H35" s="34"/>
       <c r="I35" s="27"/>
       <c r="J35" s="27"/>
       <c r="K35" s="30"/>
       <c r="L35" s="25"/>
-      <c r="M35" s="52"/>
-      <c r="O35" s="32">
+      <c r="M35" s="48"/>
+      <c r="O35" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="24.75" customHeight="1">
+    <row r="36" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="24"/>
       <c r="B36" s="25"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
       <c r="F36" s="27"/>
       <c r="G36" s="28"/>
-      <c r="H36" s="35"/>
+      <c r="H36" s="34"/>
       <c r="I36" s="27"/>
       <c r="J36" s="27"/>
       <c r="K36" s="30"/>
       <c r="L36" s="25"/>
-      <c r="M36" s="52"/>
-      <c r="O36" s="32">
+      <c r="M36" s="48"/>
+      <c r="O36" s="31">
         <f>IF(K38&gt;2,K38,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="22.5" customHeight="1">
+    <row r="37" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24"/>
       <c r="B37" s="25"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
       <c r="F37" s="27"/>
       <c r="G37" s="28"/>
-      <c r="H37" s="35"/>
+      <c r="H37" s="34"/>
       <c r="I37" s="27"/>
       <c r="J37" s="27"/>
       <c r="K37" s="30"/>
       <c r="L37" s="25"/>
-      <c r="M37" s="52"/>
-      <c r="O37" s="32">
+      <c r="M37" s="48"/>
+      <c r="O37" s="31">
         <f>IF(K37&gt;2,K37,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="27" customHeight="1">
+    <row r="38" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24"/>
       <c r="B38" s="25"/>
       <c r="C38" s="26"/>
@@ -1738,167 +1725,167 @@
       <c r="E38" s="26"/>
       <c r="F38" s="27"/>
       <c r="G38" s="28"/>
-      <c r="H38" s="35"/>
+      <c r="H38" s="34"/>
       <c r="I38" s="27"/>
       <c r="J38" s="27"/>
       <c r="K38" s="30"/>
       <c r="L38" s="25"/>
-      <c r="M38" s="52"/>
+      <c r="M38" s="48"/>
       <c r="O38" s="31">
         <f>IF(K31&gt;2,K31,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="29.25" customHeight="1">
+    <row r="39" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="24"/>
       <c r="B39" s="25"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
       <c r="F39" s="27"/>
       <c r="G39" s="28"/>
-      <c r="H39" s="37"/>
+      <c r="H39" s="34"/>
       <c r="I39" s="27"/>
       <c r="J39" s="27"/>
       <c r="K39" s="30"/>
       <c r="L39" s="25"/>
-      <c r="M39" s="52"/>
-      <c r="O39" s="32">
+      <c r="M39" s="48"/>
+      <c r="O39" s="31">
         <f>IF(K39&gt;2,K39,2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="24.75" customHeight="1">
+    <row r="40" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="24"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
       <c r="F40" s="27"/>
       <c r="G40" s="28"/>
-      <c r="H40" s="39"/>
+      <c r="H40" s="36"/>
       <c r="I40" s="27"/>
       <c r="J40" s="27"/>
       <c r="K40" s="30"/>
       <c r="L40" s="25"/>
-      <c r="M40" s="52"/>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1">
-      <c r="F41" s="33"/>
-      <c r="G41" s="40" t="s">
+      <c r="M40" s="48"/>
+    </row>
+    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F41" s="32"/>
+      <c r="G41" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="38">
         <f>SUM(H18:H39)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="42" t="s">
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="M41" s="43">
+      <c r="M41" s="40">
         <f>SUM(M18:M40)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1">
+    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3"/>
-      <c r="H42" s="44"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="47" t="s">
+      <c r="H42" s="41"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M42" s="48">
+      <c r="M42" s="45">
         <f>M41*10%</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1">
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="42" t="s">
+    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="49">
+      <c r="M43" s="46">
         <f>M41-M42</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="57.75" customHeight="1">
-      <c r="B44" s="69" t="s">
+    <row r="44" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="69"/>
-      <c r="J44" s="69"/>
-      <c r="K44" s="69"/>
-      <c r="L44" s="69"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="47"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H45" s="5"/>
     </row>
-    <row r="47" spans="1:15">
-      <c r="B47" s="70" t="s">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B47" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="H47" s="70" t="s">
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="H47" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70"/>
-    </row>
-    <row r="48" spans="1:15">
-      <c r="B48" s="71" t="s">
+      <c r="I47" s="66"/>
+      <c r="J47" s="66"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B48" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="71"/>
-      <c r="D48" s="71"/>
-      <c r="H48" s="71" t="s">
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="H48" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="I48" s="71"/>
-      <c r="J48" s="71"/>
-    </row>
-    <row r="49" spans="2:10" ht="14.25" customHeight="1">
-      <c r="B49" s="70" t="s">
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+    </row>
+    <row r="49" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="H49" s="70" t="s">
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="H49" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="I49" s="70"/>
-      <c r="J49" s="70"/>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" s="71" t="s">
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B50" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="71"/>
-      <c r="D50" s="71"/>
-      <c r="H50" s="78" t="s">
+      <c r="C50" s="67"/>
+      <c r="D50" s="67"/>
+      <c r="H50" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="I50" s="78"/>
-      <c r="J50" s="78"/>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="I50" s="74"/>
+      <c r="J50" s="74"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
         <v>42</v>
       </c>
